--- a/filter_element_2VRDS.xlsx
+++ b/filter_element_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,37 @@
         <is>
           <t>현재고</t>
         </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>사용중</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4B/L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F7701</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_2VRDS.xlsx
+++ b/filter_element_2VRDS.xlsx
@@ -480,7 +480,7 @@
         <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F2" t="b">
         <v>0</v>

--- a/filter_element_2VRDS.xlsx
+++ b/filter_element_2VRDS.xlsx
@@ -483,7 +483,7 @@
         <v>100</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_2VRDS.xlsx
+++ b/filter_element_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,32 +458,6 @@
         <is>
           <t>사용중</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>4B/L</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>F7701</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>50</v>
-      </c>
-      <c r="E2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_2VRDS.xlsx
+++ b/filter_element_2VRDS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,6 +458,32 @@
         <is>
           <t>사용중</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>4B/L</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F7702B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/filter_element_2VRDS.xlsx
+++ b/filter_element_2VRDS.xlsx
@@ -483,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
